--- a/허브누리_레시피_목록_상세_p2of6_썸네일.xlsx
+++ b/허브누리_레시피_목록_상세_p2of6_썸네일.xlsx
@@ -5139,7 +5139,7 @@
       <row>89</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="200" name="Image 200" descr="Picture"/>
@@ -5164,7 +5164,7 @@
       <row>89</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="201" name="Image 201" descr="Picture"/>
@@ -5189,7 +5189,7 @@
       <row>89</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="202" name="Image 202" descr="Picture"/>
@@ -5214,7 +5214,7 @@
       <row>89</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="203" name="Image 203" descr="Picture"/>
@@ -5239,7 +5239,7 @@
       <row>89</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="204" name="Image 204" descr="Picture"/>
@@ -5264,7 +5264,7 @@
       <row>89</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="205" name="Image 205" descr="Picture"/>
@@ -5339,7 +5339,7 @@
       <row>91</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="208" name="Image 208" descr="Picture"/>
@@ -5364,7 +5364,7 @@
       <row>91</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="209" name="Image 209" descr="Picture"/>
@@ -5389,7 +5389,7 @@
       <row>91</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="210" name="Image 210" descr="Picture"/>
@@ -5414,7 +5414,7 @@
       <row>91</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="211" name="Image 211" descr="Picture"/>
@@ -5439,7 +5439,7 @@
       <row>91</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="212" name="Image 212" descr="Picture"/>
@@ -5464,7 +5464,7 @@
       <row>91</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="213" name="Image 213" descr="Picture"/>
@@ -7914,7 +7914,7 @@
       <row>147</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="311" name="Image 311" descr="Picture"/>
@@ -8064,7 +8064,7 @@
       <row>154</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="317" name="Image 317" descr="Picture"/>
@@ -10839,7 +10839,7 @@
       <row>229</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="428" name="Image 428" descr="Picture"/>
@@ -10864,7 +10864,7 @@
       <row>229</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="429" name="Image 429" descr="Picture"/>
@@ -10889,7 +10889,7 @@
       <row>229</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="430" name="Image 430" descr="Picture"/>
@@ -10914,7 +10914,7 @@
       <row>229</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="431" name="Image 431" descr="Picture"/>
@@ -10939,7 +10939,7 @@
       <row>229</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="432" name="Image 432" descr="Picture"/>
@@ -10964,7 +10964,7 @@
       <row>229</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="433" name="Image 433" descr="Picture"/>
@@ -11164,7 +11164,7 @@
       <row>235</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="441" name="Image 441" descr="Picture"/>
@@ -11189,7 +11189,7 @@
       <row>235</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="442" name="Image 442" descr="Picture"/>
@@ -11214,7 +11214,7 @@
       <row>235</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="443" name="Image 443" descr="Picture"/>
@@ -11239,7 +11239,7 @@
       <row>235</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="444" name="Image 444" descr="Picture"/>
@@ -11564,7 +11564,7 @@
       <row>248</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="457" name="Image 457" descr="Picture"/>
@@ -12864,7 +12864,7 @@
       <row>274</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="509" name="Image 509" descr="Picture"/>
@@ -12889,7 +12889,7 @@
       <row>274</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="510" name="Image 510" descr="Picture"/>
@@ -12914,7 +12914,7 @@
       <row>274</row>
       <rowOff>2171700</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="511" name="Image 511" descr="Picture"/>
@@ -13039,7 +13039,7 @@
       <row>276</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="516" name="Image 516" descr="Picture"/>
@@ -13064,7 +13064,7 @@
       <row>276</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="517" name="Image 517" descr="Picture"/>
@@ -13089,7 +13089,7 @@
       <row>276</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="518" name="Image 518" descr="Picture"/>
@@ -13114,7 +13114,7 @@
       <row>276</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="519" name="Image 519" descr="Picture"/>
@@ -13139,7 +13139,7 @@
       <row>276</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="520" name="Image 520" descr="Picture"/>
@@ -13164,7 +13164,7 @@
       <row>276</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="521" name="Image 521" descr="Picture"/>
@@ -13189,7 +13189,7 @@
       <row>276</row>
       <rowOff>2171700</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="522" name="Image 522" descr="Picture"/>
@@ -13214,7 +13214,7 @@
       <row>276</row>
       <rowOff>2171700</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="523" name="Image 523" descr="Picture"/>
@@ -13239,7 +13239,7 @@
       <row>276</row>
       <rowOff>2171700</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="524" name="Image 524" descr="Picture"/>
@@ -13264,7 +13264,7 @@
       <row>276</row>
       <rowOff>2171700</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="525" name="Image 525" descr="Picture"/>
@@ -13289,7 +13289,7 @@
       <row>276</row>
       <rowOff>3257550</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="526" name="Image 526" descr="Picture"/>
@@ -13314,7 +13314,7 @@
       <row>276</row>
       <rowOff>3257550</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="527" name="Image 527" descr="Picture"/>
@@ -13589,7 +13589,7 @@
       <row>285</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="538" name="Image 538" descr="Picture"/>
@@ -13614,7 +13614,7 @@
       <row>285</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="539" name="Image 539" descr="Picture"/>
@@ -13639,7 +13639,7 @@
       <row>285</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="540" name="Image 540" descr="Picture"/>
@@ -16014,7 +16014,7 @@
       <row>325</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="635" name="Image 635" descr="Picture"/>
@@ -18439,7 +18439,7 @@
       <row>366</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="771525" cy="1047750"/>
+    <ext cx="781050" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="732" name="Image 732" descr="Picture"/>
@@ -19389,7 +19389,7 @@
       <row>398</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1038225"/>
+    <ext cx="1047750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="770" name="Image 770" descr="Picture"/>
